--- a/datos_limpios/dicc_arg_datos_dm2.xlsx
+++ b/datos_limpios/dicc_arg_datos_dm2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -951,7 +951,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>total_micro</t>
+          <t>total_compl</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -966,51 +966,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Peso de discapacidad ponderado para DM2 con secuelas microvasculares</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>total_macro</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0-Inf</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Peso de discapacidad ponderado para DM2 con secuelas macrovasculares</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>total_compl</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0-Inf</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Peso de discapacidad ponderado para DM2 con secuelas micro y macrovasculares</t>
+          <t>Peso de discapacidad ponderado para DM2 total</t>
         </is>
       </c>
     </row>
